--- a/ig/nr-INS-Patient/ValueSet-fr-core-practitioner-specialty.xlsx
+++ b/ig/nr-INS-Patient/ValueSet-fr-core-practitioner-specialty.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
